--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="128">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -391,14 +391,27 @@
     <t>RelatedDocument.typeCode</t>
   </si>
   <si>
+    <t xml:space="preserve">'RPLC' pour remplacement :
+Seul le remplacement au sens annulation et remplacement 
+du document référencé par la version courante du 
+document est autorisé.
+'XFRM' pour transformation :
+La relation est portée par le document CDA transformé (et 
+pas par le document de référence). 
+</t>
+  </si>
+  <si>
     <t>http://terminology.hl7.org/ValueSet/v3-xActRelationshipDocument</t>
   </si>
   <si>
     <t>RelatedDocument.parentDocument</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ParentDocument
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ParentDocument {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-parent-document}
 </t>
+  </si>
+  <si>
+    <t>Document de référence.</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1291,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -1379,7 +1392,7 @@
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1482,7 +1495,7 @@
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1904,7 +1917,9 @@
       <c r="K12" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L12" s="2"/>
+      <c r="L12" t="s" s="2">
+        <v>123</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1935,7 +1950,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -1973,10 +1988,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1999,9 +2014,11 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="L13" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>127</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2052,7 +2069,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -391,14 +391,9 @@
     <t>RelatedDocument.typeCode</t>
   </si>
   <si>
-    <t xml:space="preserve">'RPLC' pour remplacement :
-Seul le remplacement au sens annulation et remplacement 
-du document référencé par la version courante du 
-document est autorisé.
-'XFRM' pour transformation :
-La relation est portée par le document CDA transformé (et 
-pas par le document de référence). 
-</t>
+    <t>le typeCode prend la valeur :
+- 'RPLC' pour remplacement, seul le remplacement au sens annulation et remplacement du document référencé par la version courante du document est autorisé.
+- 'XFRM' pour transformation, la relation est portée par le document CDA transformé (et pas par le document de référence).</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-xActRelationshipDocument</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="129">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,6 +311,10 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
   </si>
   <si>
     <t>RelatedDocument.typeId.nullFlavor</t>
@@ -1262,7 +1266,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1270,10 +1274,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1371,17 +1375,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1399,11 +1403,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1454,7 +1458,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1474,17 +1478,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1502,11 +1506,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1557,7 +1561,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1577,17 +1581,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1605,11 +1609,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1618,7 +1622,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1660,7 +1664,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1680,17 +1684,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1708,11 +1712,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1763,7 +1767,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1783,10 +1787,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1813,7 +1817,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1864,7 +1868,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1884,10 +1888,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1913,7 +1917,7 @@
         <v>85</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -1945,7 +1949,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -1963,7 +1967,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -1983,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2009,10 +2013,10 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -2064,7 +2068,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>RelatedDocument référence un document existant (à remplacer ou transformé).</t>
+    <t>L'élément de l'en-tête du CDA relatedDocument permet de référencer un document existant (à remplacer ou transformé).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-related-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
